--- a/artfynd/A 58387-2023 artfynd.xlsx
+++ b/artfynd/A 58387-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58387-2023 artfynd.xlsx
+++ b/artfynd/A 58387-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113698304</v>
+        <v>113698303</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,33 +703,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mjötjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422270</v>
+        <v>422738</v>
       </c>
       <c r="R2" t="n">
-        <v>7040775</v>
+        <v>7041041</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113698303</v>
+        <v>113698293</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422738</v>
+        <v>422580</v>
       </c>
       <c r="R3" t="n">
-        <v>7041041</v>
+        <v>7041095</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113698296</v>
+        <v>113698294</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422492</v>
+        <v>422445</v>
       </c>
       <c r="R4" t="n">
-        <v>7040991</v>
+        <v>7041003</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113698300</v>
+        <v>113698295</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422797</v>
+        <v>422387</v>
       </c>
       <c r="R5" t="n">
-        <v>7041047</v>
+        <v>7040942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113698301</v>
+        <v>113698296</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422723</v>
+        <v>422492</v>
       </c>
       <c r="R6" t="n">
-        <v>7041074</v>
+        <v>7040991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113698295</v>
+        <v>113698297</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422387</v>
+        <v>422545</v>
       </c>
       <c r="R7" t="n">
-        <v>7040942</v>
+        <v>7041011</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113698297</v>
+        <v>113698298</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422545</v>
+        <v>422599</v>
       </c>
       <c r="R8" t="n">
-        <v>7041011</v>
+        <v>7041000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113698293</v>
+        <v>113698299</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422580</v>
+        <v>422579</v>
       </c>
       <c r="R9" t="n">
-        <v>7041095</v>
+        <v>7040994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113698294</v>
+        <v>113698300</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422445</v>
+        <v>422797</v>
       </c>
       <c r="R10" t="n">
-        <v>7041003</v>
+        <v>7041047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,6 +1590,221 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113698301</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mjötjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>422723</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7041074</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113698304</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mjötjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>422270</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7040775</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58387-2023 artfynd.xlsx
+++ b/artfynd/A 58387-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698303</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698293</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698294</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698295</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698296</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698297</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698298</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698300</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698301</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,8 +1860,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113698304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>